--- a/python_backend/template_converted.xlsx
+++ b/python_backend/template_converted.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Nomencladores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listado de Gastos'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listado de Gastos'!$A$1:$AE$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,25 +28,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,51 +416,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.7109375" customWidth="1" min="1" max="1"/>
+    <col width="30.7109375" customWidth="1" min="2" max="2"/>
+    <col width="43.42578125" customWidth="1" min="3" max="3"/>
+    <col width="30.7109375" customWidth="1" min="4" max="4"/>
+    <col width="30.7109375" customWidth="1" min="5" max="5"/>
+    <col width="30.7109375" customWidth="1" min="6" max="6"/>
+    <col width="30.7109375" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20.7109375" customWidth="1" min="9" max="9"/>
+    <col width="20.7109375" customWidth="1" min="10" max="10"/>
+    <col width="20.7109375" customWidth="1" min="11" max="11"/>
+    <col width="20.7109375" customWidth="1" min="12" max="12"/>
+    <col width="30.7109375" customWidth="1" min="13" max="13"/>
+    <col width="30.7109375" customWidth="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" min="15" max="15"/>
+    <col width="30.7109375" customWidth="1" min="16" max="16"/>
+    <col width="30.7109375" customWidth="1" min="17" max="17"/>
+    <col width="30.7109375" customWidth="1" min="18" max="18"/>
+    <col width="30.7109375" customWidth="1" min="19" max="19"/>
+    <col width="30.7109375" customWidth="1" min="20" max="20"/>
+    <col width="30.7109375" customWidth="1" min="21" max="21"/>
+    <col width="30.7109375" customWidth="1" min="22" max="22"/>
+    <col width="12.7109375" customWidth="1" min="23" max="23"/>
+    <col width="11.5703125" customWidth="1" min="24" max="24"/>
+    <col width="11.5703125" customWidth="1" min="25" max="25"/>
+    <col width="11.5703125" customWidth="1" min="26" max="26"/>
+    <col width="11.5703125" customWidth="1" min="27" max="27"/>
+    <col width="11.5703125" customWidth="1" min="28" max="28"/>
+    <col width="11.5703125" customWidth="1" min="29" max="29"/>
+    <col width="11.5703125" customWidth="1" min="30" max="30"/>
+    <col width="11.5703125" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Tipo de Suplidor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Gasto</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo de Gasto </t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Decripcion</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Monto en Servicios</t>
-        </is>
-      </c>
-    </row>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monto en Servicios </t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Monto en Bienes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ITBIS</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SELECTIVO</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>OTROS IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Impuesto 4</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Impuesto 5</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Forma de Pago</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Concepto Id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Tipo de Pago Id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>NCF</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>NCF Afectado</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Retencion ITBIS</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Retencion ISR</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Llevar ITBIS al Costo</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Aplica Proporcionalidad del ITBIS</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: LEER ESTA NOTA ANTES DE LLENAR LA PLANTILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Antes de iniciar el proceso para completar la plantilla de Carga Masiva de Gastos, debe verificar los comentarios que se encuentran en la cabecera de cada columna (colocar el cursor encima de la cabecera de la columna deseada), que describe los detalles necesarios para saber que información colocar en cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1"/>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="15" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:AE1"/>
+  <mergeCells count="2">
+    <mergeCell ref="X1:AE1"/>
+    <mergeCell ref="X2:AE6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -489,18 +596,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.7109375" customWidth="1" min="1" max="1"/>
+    <col width="9.7109375" customWidth="1" min="2" max="2"/>
+    <col width="14.5703125" customWidth="1" min="3" max="3"/>
+    <col width="10.7109375" customWidth="1" min="4" max="4"/>
+    <col width="43.7109375" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" customWidth="1" min="6" max="6"/>
+    <col width="34.28515625" customWidth="1" min="7" max="7"/>
+    <col width="9.140625" customWidth="1" min="8" max="8"/>
+    <col width="16.5703125" customWidth="1" min="9" max="9"/>
+    <col width="9.140625" customWidth="1" min="10" max="10"/>
+    <col width="93.5703125" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Tipo de Suplidor</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Tipo de Gasto</t>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>TipoSuplidor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TipoGasto</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>FormaPago</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Retenciones Itbis</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>RetencionISR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gasto Formal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01-Gasto de personal</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EFECTIVO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ITBIS-30%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ISR-10% - Alquileres - COD. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gasto Informal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02-Gastos por trabajos, servicios y suministros</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CHEQUES/TRANSFERENCIAS/DEPÓSITO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ITBIS-75%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ISR-10% - Honorarios Por Servicio - COD. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Genérico</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>03-Arrendamientos</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TARJETA CRÉDITO/DÉBITO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ITBIS-100%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ISR-25% - Premios de Lotería - COD. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gasto Menor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04-Gastos de activo fijo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMPRA A CREDITO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ISR-2% - Transferencia Títulos - COD. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pagos al exterior</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>05-Gastos de representación</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PERMUTA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ISR-10% - Dividendos - COD. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Norma 07-2007</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>06-Otras deducciones administrativas</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NOTA DE CREDITO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ISR-10% - Intereses a Personas Jurídicas o Entidades no residentes (Ley 253-12) - COD. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DGA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>07-Gastos financieros</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ISR-5% - Intereses a Personas Jurídicas o Entidades no residentes (Ley 57-2007) - COD. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Decreto 139-98</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>08-Gastos extraordinarios</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ISR-10% - Intereses a Personas Físicas no residentes (Ley 253-12) - COD. 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>09-Compras y gastos que forman gastos de la venta</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ISR-5% - Intereses a Personas Físicas no residentes (Leyes 57-2007 y 253-12) - COD. 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10-Adquisicion de activos</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ISR-27% - Remesas - COD. 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>11-Gastos de seguros</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ISR-5% - Retención por pago proveedores del estado - COD. 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ISR-5% - Juegos Telefónicos (Norma 08-2011) - COD. 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ISR-1% - Ganancia de Capital (Norma 07-2011) - COD. 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ISR-10% - Otras Rentas - COD. 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ISR-2% - Otras Retenciones - COD. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ISR-1% - Intereses Pagados por Entidades Financieras a Personas Jurídicas Residentes (Norma 13-2011) - COD. 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ISR-10% - Intereses Pagados por Entidades Financieras a Personas Físicas Residentes (Ley 253-12) - COD. 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ISR-2% - Servicios Técnicos - COD. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ISR-2% - Retención Decreto 139-98 - COD. 16</t>
         </is>
       </c>
     </row>

--- a/python_backend/template_converted.xlsx
+++ b/python_backend/template_converted.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Nomencladores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listado de Gastos'!$A$1:$AE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listado de Gastos'!$A$1:$AF$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,175 +416,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.7109375" customWidth="1" min="1" max="1"/>
-    <col width="30.7109375" customWidth="1" min="2" max="2"/>
-    <col width="43.42578125" customWidth="1" min="3" max="3"/>
-    <col width="30.7109375" customWidth="1" min="4" max="4"/>
-    <col width="30.7109375" customWidth="1" min="5" max="5"/>
-    <col width="30.7109375" customWidth="1" min="6" max="6"/>
-    <col width="30.7109375" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20.7109375" customWidth="1" min="9" max="9"/>
-    <col width="20.7109375" customWidth="1" min="10" max="10"/>
-    <col width="20.7109375" customWidth="1" min="11" max="11"/>
-    <col width="20.7109375" customWidth="1" min="12" max="12"/>
-    <col width="30.7109375" customWidth="1" min="13" max="13"/>
-    <col width="30.7109375" customWidth="1" min="14" max="14"/>
-    <col width="30.7109375" customWidth="1" min="15" max="15"/>
-    <col width="30.7109375" customWidth="1" min="16" max="16"/>
-    <col width="30.7109375" customWidth="1" min="17" max="17"/>
-    <col width="30.7109375" customWidth="1" min="18" max="18"/>
-    <col width="30.7109375" customWidth="1" min="19" max="19"/>
-    <col width="30.7109375" customWidth="1" min="20" max="20"/>
-    <col width="30.7109375" customWidth="1" min="21" max="21"/>
-    <col width="30.7109375" customWidth="1" min="22" max="22"/>
-    <col width="12.7109375" customWidth="1" min="23" max="23"/>
-    <col width="11.5703125" customWidth="1" min="24" max="24"/>
-    <col width="11.5703125" customWidth="1" min="25" max="25"/>
-    <col width="11.5703125" customWidth="1" min="26" max="26"/>
-    <col width="11.5703125" customWidth="1" min="27" max="27"/>
-    <col width="11.5703125" customWidth="1" min="28" max="28"/>
-    <col width="11.5703125" customWidth="1" min="29" max="29"/>
-    <col width="11.5703125" customWidth="1" min="30" max="30"/>
-    <col width="11.5703125" customWidth="1" min="31" max="31"/>
+    <col width="11.54296875" customWidth="1" min="1" max="1"/>
+    <col width="30.81640625" customWidth="1" min="2" max="2"/>
+    <col width="30.81640625" customWidth="1" min="3" max="3"/>
+    <col width="43.453125" customWidth="1" min="4" max="4"/>
+    <col width="30.81640625" customWidth="1" min="5" max="5"/>
+    <col width="30.81640625" customWidth="1" min="6" max="6"/>
+    <col width="30.81640625" customWidth="1" min="7" max="7"/>
+    <col width="30.81640625" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20.81640625" customWidth="1" min="10" max="10"/>
+    <col width="20.81640625" customWidth="1" min="11" max="11"/>
+    <col width="20.81640625" customWidth="1" min="12" max="12"/>
+    <col width="20.81640625" customWidth="1" min="13" max="13"/>
+    <col width="30.81640625" customWidth="1" min="14" max="14"/>
+    <col width="30.81640625" customWidth="1" min="15" max="15"/>
+    <col width="30.81640625" customWidth="1" min="16" max="16"/>
+    <col width="30.81640625" customWidth="1" min="17" max="17"/>
+    <col width="30.81640625" customWidth="1" min="18" max="18"/>
+    <col width="30.81640625" customWidth="1" min="19" max="19"/>
+    <col width="30.81640625" customWidth="1" min="20" max="20"/>
+    <col width="30.81640625" customWidth="1" min="21" max="21"/>
+    <col width="30.81640625" customWidth="1" min="22" max="22"/>
+    <col width="30.81640625" customWidth="1" min="23" max="23"/>
+    <col width="12.6328125" customWidth="1" min="24" max="24"/>
+    <col width="11.54296875" customWidth="1" min="25" max="25"/>
+    <col width="11.54296875" customWidth="1" min="26" max="26"/>
+    <col width="11.54296875" customWidth="1" min="27" max="27"/>
+    <col width="11.54296875" customWidth="1" min="28" max="28"/>
+    <col width="11.54296875" customWidth="1" min="29" max="29"/>
+    <col width="11.54296875" customWidth="1" min="30" max="30"/>
+    <col width="11.54296875" customWidth="1" min="31" max="31"/>
+    <col width="11.54296875" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
+    <row r="1" ht="18.5" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo de Suplidor</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo de Gasto </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Decripcion</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Monto en Servicios </t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Monto en Bienes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ITBIS</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>SELECTIVO</t>
+          <t>Impuesto 1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>OTROS IMPUESTOS</t>
+          <t>Impuesto 2</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Impuesto 3</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Impuesto 4</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Impuesto 5</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Forma de Pago</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Concepto Id</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Tipo de Pago Id</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NCF</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>NCF Afectado</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Retencion ITBIS</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Retencion ISR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Llevar ITBIS al Costo</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Aplica Proporcionalidad del ITBIS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>IMPORTANTE: LEER ESTA NOTA ANTES DE LLENAR LA PLANTILLA</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="X2" t="inlineStr">
+    <row r="2" ht="14.5" customHeight="1">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Antes de iniciar el proceso para completar la plantilla de Carga Masiva de Gastos, debe verificar los comentarios que se encuentran en la cabecera de cada columna (colocar el cursor encima de la cabecera de la columna deseada), que describe los detalles necesarios para saber que información colocar en cada una.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1"/>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1"/>
-    <row r="6" ht="15" customHeight="1"/>
+    <row r="3" ht="14.5" customHeight="1"/>
+    <row r="4" ht="14.5" customHeight="1"/>
+    <row r="5" ht="14.5" customHeight="1"/>
+    <row r="6" ht="14.5" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:AE1"/>
+  <autoFilter ref="A1:AF1"/>
   <mergeCells count="2">
-    <mergeCell ref="X1:AE1"/>
-    <mergeCell ref="X2:AE6"/>
+    <mergeCell ref="Y2:AF6"/>
+    <mergeCell ref="Y1:AF1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -599,20 +605,20 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.7109375" customWidth="1" min="1" max="1"/>
-    <col width="9.7109375" customWidth="1" min="2" max="2"/>
-    <col width="14.5703125" customWidth="1" min="3" max="3"/>
-    <col width="10.7109375" customWidth="1" min="4" max="4"/>
-    <col width="43.7109375" customWidth="1" min="5" max="5"/>
-    <col width="10.7109375" customWidth="1" min="6" max="6"/>
-    <col width="34.28515625" customWidth="1" min="7" max="7"/>
-    <col width="9.140625" customWidth="1" min="8" max="8"/>
-    <col width="16.5703125" customWidth="1" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" min="10" max="10"/>
-    <col width="93.5703125" customWidth="1" min="11" max="11"/>
+    <col width="10.6328125" customWidth="1" min="1" max="1"/>
+    <col width="9.81640625" customWidth="1" min="2" max="2"/>
+    <col width="14.54296875" customWidth="1" min="3" max="3"/>
+    <col width="10.81640625" customWidth="1" min="4" max="4"/>
+    <col width="43.81640625" customWidth="1" min="5" max="5"/>
+    <col width="10.81640625" customWidth="1" min="6" max="6"/>
+    <col width="34.1796875" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16.54296875" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="93.54296875" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Confirmar</t>
@@ -644,7 +650,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="14.5" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Si</t>
@@ -676,7 +682,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>No</t>
@@ -708,7 +714,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Genérico</t>
@@ -735,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="14.5" customHeight="1">
       <c r="C5" t="inlineStr">
         <is>
           <t>Gasto Menor</t>
@@ -757,7 +763,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="14.5" customHeight="1">
       <c r="C6" t="inlineStr">
         <is>
           <t>Pagos al exterior</t>
@@ -779,7 +785,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="14.5" customHeight="1">
       <c r="C7" t="inlineStr">
         <is>
           <t>Norma 07-2007</t>
@@ -801,7 +807,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="C8" t="inlineStr">
         <is>
           <t>DGA</t>
@@ -823,7 +829,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="C9" t="inlineStr">
         <is>
           <t>Decreto 139-98</t>
@@ -840,7 +846,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="14.5" customHeight="1">
       <c r="E10" t="inlineStr">
         <is>
           <t>09-Compras y gastos que forman gastos de la venta</t>
@@ -852,7 +858,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="14.5" customHeight="1">
       <c r="E11" t="inlineStr">
         <is>
           <t>10-Adquisicion de activos</t>
@@ -864,7 +870,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15" customHeight="1">
       <c r="E12" t="inlineStr">
         <is>
           <t>11-Gastos de seguros</t>
@@ -876,56 +882,56 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="14.5" customHeight="1">
       <c r="K13" t="inlineStr">
         <is>
           <t>ISR-5% - Juegos Telefónicos (Norma 08-2011) - COD. 13</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="14.5" customHeight="1">
       <c r="K14" t="inlineStr">
         <is>
           <t>ISR-1% - Ganancia de Capital (Norma 07-2011) - COD. 14</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="14.5" customHeight="1">
       <c r="K15" t="inlineStr">
         <is>
           <t>ISR-10% - Otras Rentas - COD. 15</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="14.5" customHeight="1">
       <c r="K16" t="inlineStr">
         <is>
           <t>ISR-2% - Otras Retenciones - COD. 16</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="14.5" customHeight="1">
       <c r="K17" t="inlineStr">
         <is>
           <t>ISR-1% - Intereses Pagados por Entidades Financieras a Personas Jurídicas Residentes (Norma 13-2011) - COD. 17</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="14.5" customHeight="1">
       <c r="K18" t="inlineStr">
         <is>
           <t>ISR-10% - Intereses Pagados por Entidades Financieras a Personas Físicas Residentes (Ley 253-12) - COD. 18</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="14.5" customHeight="1">
       <c r="K19" t="inlineStr">
         <is>
           <t>ISR-2% - Servicios Técnicos - COD. 16</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="K20" t="inlineStr">
         <is>
           <t>ISR-2% - Retención Decreto 139-98 - COD. 16</t>
